--- a/main/ig/StructureDefinition-dmi-organization-ej.xlsx
+++ b/main/ig/StructureDefinition-dmi-organization-ej.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.0.0</t>
+    <t>3.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-27T10:37:28+00:00</t>
+    <t>2026-03-05T09:47:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-dmi-organization-ej.xlsx
+++ b/main/ig/StructureDefinition-dmi-organization-ej.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T09:47:44+00:00</t>
+    <t>2026-03-05T10:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-dmi-organization-ej.xlsx
+++ b/main/ig/StructureDefinition-dmi-organization-ej.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6047" uniqueCount="643">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6049" uniqueCount="646">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T10:00:25+00:00</t>
+    <t>2026-03-05T10:01:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1431,11 +1431,23 @@
     <t>Organization.identifier:numeroTVAIntracommunautaire.period</t>
   </si>
   <si>
+    <t>A Period specifies a range of time; the context of use will specify whether the entire range applies (e.g. "the patient was an inpatient of the hospital for this time range") or one value from the range applies (e.g. "give to the patient between these two times").
+Period is not used for a duration (a measure of elapsed time). See [Duration](http://hl7.org/fhir/R4/datatypes.html#Duration).</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+per-1:If present, start SHALL have a lower value than end {start.hasValue().not() or end.hasValue().not() or (start &lt;= end)}</t>
+  </si>
+  <si>
     <t>Organization.identifier:numeroTVAIntracommunautaire.assigner</t>
   </si>
   <si>
     <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
   </si>
   <si>
     <t>Organization.identifier:numeroSRN</t>
@@ -12988,7 +13000,7 @@
         <v>79</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="AJ93" t="s" s="2">
         <v>116</v>
@@ -12997,7 +13009,7 @@
         <v>77</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>105</v>
+        <v>190</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>77</v>
@@ -13104,7 +13116,7 @@
         <v>87</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="AJ94" t="s" s="2">
         <v>99</v>
@@ -13220,7 +13232,7 @@
         <v>87</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="AJ95" t="s" s="2">
         <v>99</v>
@@ -13336,7 +13348,7 @@
         <v>87</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="AJ96" t="s" s="2">
         <v>99</v>
@@ -13450,7 +13462,7 @@
         <v>87</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="AJ97" t="s" s="2">
         <v>99</v>
@@ -13504,7 +13516,9 @@
       <c r="M98" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="N98" s="2"/>
+      <c r="N98" t="s" s="2">
+        <v>452</v>
+      </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>77</v>
@@ -13562,10 +13576,10 @@
         <v>87</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>99</v>
+        <v>453</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>295</v>
@@ -13582,7 +13596,7 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B99" t="s" s="2">
         <v>299</v>
@@ -13608,7 +13622,7 @@
         <v>88</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="L99" t="s" s="2">
         <v>301</v>
@@ -13676,10 +13690,10 @@
         <v>87</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>99</v>
+        <v>456</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>305</v>
@@ -13696,13 +13710,13 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="B100" t="s" s="2">
         <v>223</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D100" t="s" s="2">
         <v>77</v>
@@ -13812,7 +13826,7 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="B101" t="s" s="2">
         <v>240</v>
@@ -13924,7 +13938,7 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="B102" t="s" s="2">
         <v>242</v>
@@ -14018,7 +14032,7 @@
         <v>79</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="AJ102" t="s" s="2">
         <v>116</v>
@@ -14027,7 +14041,7 @@
         <v>77</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>105</v>
+        <v>190</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>77</v>
@@ -14038,7 +14052,7 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="B103" t="s" s="2">
         <v>244</v>
@@ -14134,7 +14148,7 @@
         <v>87</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="AJ103" t="s" s="2">
         <v>99</v>
@@ -14154,7 +14168,7 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="B104" t="s" s="2">
         <v>256</v>
@@ -14202,7 +14216,7 @@
         <v>77</v>
       </c>
       <c r="S104" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="T104" t="s" s="2">
         <v>77</v>
@@ -14250,7 +14264,7 @@
         <v>87</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="AJ104" t="s" s="2">
         <v>99</v>
@@ -14270,7 +14284,7 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="B105" t="s" s="2">
         <v>268</v>
@@ -14366,7 +14380,7 @@
         <v>87</v>
       </c>
       <c r="AI105" t="s" s="2">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="AJ105" t="s" s="2">
         <v>99</v>
@@ -14386,7 +14400,7 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="B106" t="s" s="2">
         <v>280</v>
@@ -14480,7 +14494,7 @@
         <v>87</v>
       </c>
       <c r="AI106" t="s" s="2">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="AJ106" t="s" s="2">
         <v>99</v>
@@ -14500,7 +14514,7 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="B107" t="s" s="2">
         <v>290</v>
@@ -14534,7 +14548,9 @@
       <c r="M107" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="N107" s="2"/>
+      <c r="N107" t="s" s="2">
+        <v>452</v>
+      </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
         <v>77</v>
@@ -14592,10 +14608,10 @@
         <v>87</v>
       </c>
       <c r="AI107" t="s" s="2">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>99</v>
+        <v>453</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>295</v>
@@ -14612,7 +14628,7 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="B108" t="s" s="2">
         <v>299</v>
@@ -14638,7 +14654,7 @@
         <v>88</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="L108" t="s" s="2">
         <v>301</v>
@@ -14706,10 +14722,10 @@
         <v>87</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>99</v>
+        <v>456</v>
       </c>
       <c r="AK108" t="s" s="2">
         <v>305</v>
@@ -14726,10 +14742,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14755,67 +14771,67 @@
         <v>394</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="N109" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="O109" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="P109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q109" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="R109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF109" t="s" s="2">
         <v>468</v>
-      </c>
-      <c r="O109" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="P109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q109" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="R109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF109" t="s" s="2">
-        <v>465</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>78</v>
@@ -14830,24 +14846,24 @@
         <v>99</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14873,16 +14889,16 @@
         <v>257</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>77</v>
@@ -14910,16 +14926,16 @@
         <v>157</v>
       </c>
       <c r="Y110" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="Z110" t="s" s="2">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB110" t="s" s="2">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="AC110" s="2"/>
       <c r="AD110" t="s" s="2">
@@ -14929,7 +14945,7 @@
         <v>114</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>78</v>
@@ -14944,27 +14960,27 @@
         <v>99</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="D111" t="s" s="2">
         <v>77</v>
@@ -14989,16 +15005,16 @@
         <v>257</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>77</v>
@@ -15027,7 +15043,7 @@
       </c>
       <c r="Y111" s="2"/>
       <c r="Z111" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>77</v>
@@ -15045,7 +15061,7 @@
         <v>77</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>78</v>
@@ -15060,24 +15076,24 @@
         <v>99</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15186,10 +15202,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15300,10 +15316,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15416,10 +15432,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15528,10 +15544,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15642,10 +15658,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15758,10 +15774,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -15872,10 +15888,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -15901,7 +15917,7 @@
         <v>167</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="M119" t="s" s="2">
         <v>379</v>
@@ -15986,10 +16002,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16100,10 +16116,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16216,10 +16232,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16332,13 +16348,13 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="D123" t="s" s="2">
         <v>77</v>
@@ -16363,16 +16379,16 @@
         <v>257</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="O123" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>77</v>
@@ -16401,7 +16417,7 @@
       </c>
       <c r="Y123" s="2"/>
       <c r="Z123" t="s" s="2">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="AA123" t="s" s="2">
         <v>77</v>
@@ -16419,7 +16435,7 @@
         <v>77</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>78</v>
@@ -16434,24 +16450,24 @@
         <v>99</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="AM123" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16560,10 +16576,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -16674,10 +16690,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16790,10 +16806,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -16902,10 +16918,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17016,10 +17032,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17132,10 +17148,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17246,10 +17262,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17275,7 +17291,7 @@
         <v>167</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="M131" t="s" s="2">
         <v>379</v>
@@ -17360,10 +17376,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17474,10 +17490,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -17590,10 +17606,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -17706,13 +17722,13 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="C135" t="s" s="2">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="D135" t="s" s="2">
         <v>77</v>
@@ -17737,16 +17753,16 @@
         <v>257</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="O135" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>77</v>
@@ -17775,7 +17791,7 @@
       </c>
       <c r="Y135" s="2"/>
       <c r="Z135" t="s" s="2">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="AA135" t="s" s="2">
         <v>77</v>
@@ -17793,7 +17809,7 @@
         <v>77</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>78</v>
@@ -17808,24 +17824,24 @@
         <v>99</v>
       </c>
       <c r="AK135" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="AL135" t="s" s="2">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="AM135" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AN135" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -17934,10 +17950,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18048,10 +18064,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18164,10 +18180,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18276,10 +18292,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -18390,10 +18406,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -18506,10 +18522,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -18620,10 +18636,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -18649,7 +18665,7 @@
         <v>167</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="M143" t="s" s="2">
         <v>379</v>
@@ -18734,10 +18750,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -18848,10 +18864,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -18964,10 +18980,10 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -19080,10 +19096,10 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -19109,16 +19125,16 @@
         <v>101</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="O147" t="s" s="2">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>77</v>
@@ -19167,7 +19183,7 @@
         <v>77</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>78</v>
@@ -19182,13 +19198,13 @@
         <v>99</v>
       </c>
       <c r="AK147" t="s" s="2">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="AL147" t="s" s="2">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="AM147" t="s" s="2">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="AN147" t="s" s="2">
         <v>77</v>
@@ -19196,10 +19212,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -19225,16 +19241,16 @@
         <v>101</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="O148" t="s" s="2">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>77</v>
@@ -19283,7 +19299,7 @@
         <v>77</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>78</v>
@@ -19301,7 +19317,7 @@
         <v>77</v>
       </c>
       <c r="AL148" t="s" s="2">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="AM148" t="s" s="2">
         <v>77</v>
@@ -19312,10 +19328,10 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -19338,19 +19354,19 @@
         <v>77</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="O149" t="s" s="2">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>77</v>
@@ -19399,7 +19415,7 @@
         <v>77</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>78</v>
@@ -19411,16 +19427,16 @@
         <v>199</v>
       </c>
       <c r="AJ149" t="s" s="2">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="AK149" t="s" s="2">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="AL149" t="s" s="2">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="AM149" t="s" s="2">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="AN149" t="s" s="2">
         <v>77</v>
@@ -19428,10 +19444,10 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -19454,19 +19470,19 @@
         <v>77</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="O150" t="s" s="2">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="P150" t="s" s="2">
         <v>77</v>
@@ -19515,7 +19531,7 @@
         <v>77</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>78</v>
@@ -19527,16 +19543,16 @@
         <v>199</v>
       </c>
       <c r="AJ150" t="s" s="2">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="AK150" t="s" s="2">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="AL150" t="s" s="2">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="AM150" t="s" s="2">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="AN150" t="s" s="2">
         <v>77</v>
@@ -19544,10 +19560,10 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -19570,17 +19586,17 @@
         <v>88</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="N151" s="2"/>
       <c r="O151" t="s" s="2">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="P151" t="s" s="2">
         <v>77</v>
@@ -19629,7 +19645,7 @@
         <v>77</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>78</v>
@@ -19644,10 +19660,10 @@
         <v>99</v>
       </c>
       <c r="AK151" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="AL151" t="s" s="2">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="AM151" t="s" s="2">
         <v>105</v>
@@ -19658,10 +19674,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -19770,10 +19786,10 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -19884,10 +19900,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -19913,13 +19929,13 @@
         <v>101</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="O154" s="2"/>
       <c r="P154" t="s" s="2">
@@ -19969,7 +19985,7 @@
         <v>77</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>78</v>
@@ -19978,7 +19994,7 @@
         <v>87</v>
       </c>
       <c r="AI154" t="s" s="2">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="AJ154" t="s" s="2">
         <v>99</v>
@@ -19998,10 +20014,10 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -20027,13 +20043,13 @@
         <v>129</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="O155" s="2"/>
       <c r="P155" t="s" s="2">
@@ -20063,7 +20079,7 @@
       </c>
       <c r="Y155" s="2"/>
       <c r="Z155" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="AA155" t="s" s="2">
         <v>77</v>
@@ -20081,7 +20097,7 @@
         <v>77</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>78</v>
@@ -20110,10 +20126,10 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -20139,13 +20155,13 @@
         <v>225</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="O156" s="2"/>
       <c r="P156" t="s" s="2">
@@ -20195,7 +20211,7 @@
         <v>77</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>78</v>
@@ -20213,7 +20229,7 @@
         <v>77</v>
       </c>
       <c r="AL156" t="s" s="2">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="AM156" t="s" s="2">
         <v>77</v>
@@ -20224,10 +20240,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -20253,13 +20269,13 @@
         <v>101</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="O157" s="2"/>
       <c r="P157" t="s" s="2">
@@ -20309,7 +20325,7 @@
         <v>77</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>78</v>
@@ -20338,10 +20354,10 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -20364,19 +20380,19 @@
         <v>77</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="O158" t="s" s="2">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="P158" t="s" s="2">
         <v>77</v>
@@ -20425,7 +20441,7 @@
         <v>77</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>78</v>
@@ -20443,7 +20459,7 @@
         <v>77</v>
       </c>
       <c r="AL158" t="s" s="2">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="AM158" t="s" s="2">
         <v>77</v>
@@ -20454,10 +20470,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -20566,10 +20582,10 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -20680,14 +20696,14 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="E161" s="2"/>
       <c r="F161" t="s" s="2">
@@ -20709,10 +20725,10 @@
         <v>108</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="N161" t="s" s="2">
         <v>111</v>
@@ -20767,7 +20783,7 @@
         <v>77</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>78</v>
@@ -20796,10 +20812,10 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -20825,14 +20841,14 @@
         <v>257</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" t="s" s="2">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="P162" t="s" s="2">
         <v>77</v>
@@ -20860,10 +20876,10 @@
         <v>149</v>
       </c>
       <c r="Y162" t="s" s="2">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="Z162" t="s" s="2">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="AA162" t="s" s="2">
         <v>77</v>
@@ -20881,7 +20897,7 @@
         <v>77</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>78</v>
@@ -20899,7 +20915,7 @@
         <v>77</v>
       </c>
       <c r="AL162" t="s" s="2">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="AM162" t="s" s="2">
         <v>77</v>
@@ -20910,10 +20926,10 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -20936,17 +20952,17 @@
         <v>77</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="N163" s="2"/>
       <c r="O163" t="s" s="2">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>77</v>
@@ -20995,7 +21011,7 @@
         <v>77</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>78</v>
@@ -21010,10 +21026,10 @@
         <v>99</v>
       </c>
       <c r="AK163" t="s" s="2">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="AL163" t="s" s="2">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="AM163" t="s" s="2">
         <v>77</v>
@@ -21024,10 +21040,10 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -21050,17 +21066,17 @@
         <v>77</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="N164" s="2"/>
       <c r="O164" t="s" s="2">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="P164" t="s" s="2">
         <v>77</v>
@@ -21109,7 +21125,7 @@
         <v>77</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>78</v>
@@ -21121,16 +21137,16 @@
         <v>199</v>
       </c>
       <c r="AJ164" t="s" s="2">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="AK164" t="s" s="2">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="AL164" t="s" s="2">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="AM164" t="s" s="2">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="AN164" t="s" s="2">
         <v>77</v>
@@ -21138,10 +21154,10 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -21164,19 +21180,19 @@
         <v>77</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="O165" t="s" s="2">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="P165" t="s" s="2">
         <v>77</v>
@@ -21225,7 +21241,7 @@
         <v>77</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>78</v>
@@ -21240,13 +21256,13 @@
         <v>99</v>
       </c>
       <c r="AK165" t="s" s="2">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="AL165" t="s" s="2">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="AM165" t="s" s="2">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="AN165" t="s" s="2">
         <v>77</v>
@@ -21254,10 +21270,10 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -21280,17 +21296,17 @@
         <v>77</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" t="s" s="2">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="P166" t="s" s="2">
         <v>77</v>
@@ -21339,7 +21355,7 @@
         <v>77</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>78</v>

--- a/main/ig/StructureDefinition-dmi-organization-ej.xlsx
+++ b/main/ig/StructureDefinition-dmi-organization-ej.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6049" uniqueCount="646">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6047" uniqueCount="643">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T10:01:25+00:00</t>
+    <t>2026-03-05T10:22:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1431,23 +1431,11 @@
     <t>Organization.identifier:numeroTVAIntracommunautaire.period</t>
   </si>
   <si>
-    <t>A Period specifies a range of time; the context of use will specify whether the entire range applies (e.g. "the patient was an inpatient of the hospital for this time range") or one value from the range applies (e.g. "give to the patient between these two times").
-Period is not used for a duration (a measure of elapsed time). See [Duration](http://hl7.org/fhir/R4/datatypes.html#Duration).</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-per-1:If present, start SHALL have a lower value than end {start.hasValue().not() or end.hasValue().not() or (start &lt;= end)}</t>
-  </si>
-  <si>
     <t>Organization.identifier:numeroTVAIntracommunautaire.assigner</t>
   </si>
   <si>
     <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
   </si>
   <si>
     <t>Organization.identifier:numeroSRN</t>
@@ -13000,7 +12988,7 @@
         <v>79</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>199</v>
+        <v>77</v>
       </c>
       <c r="AJ93" t="s" s="2">
         <v>116</v>
@@ -13009,7 +12997,7 @@
         <v>77</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>190</v>
+        <v>105</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>77</v>
@@ -13116,7 +13104,7 @@
         <v>87</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>199</v>
+        <v>77</v>
       </c>
       <c r="AJ94" t="s" s="2">
         <v>99</v>
@@ -13232,7 +13220,7 @@
         <v>87</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>199</v>
+        <v>77</v>
       </c>
       <c r="AJ95" t="s" s="2">
         <v>99</v>
@@ -13348,7 +13336,7 @@
         <v>87</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>199</v>
+        <v>77</v>
       </c>
       <c r="AJ96" t="s" s="2">
         <v>99</v>
@@ -13462,7 +13450,7 @@
         <v>87</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>199</v>
+        <v>77</v>
       </c>
       <c r="AJ97" t="s" s="2">
         <v>99</v>
@@ -13516,9 +13504,7 @@
       <c r="M98" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="N98" t="s" s="2">
-        <v>452</v>
-      </c>
+      <c r="N98" s="2"/>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>77</v>
@@ -13576,10 +13562,10 @@
         <v>87</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>199</v>
+        <v>77</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>453</v>
+        <v>99</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>295</v>
@@ -13596,7 +13582,7 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="B99" t="s" s="2">
         <v>299</v>
@@ -13622,7 +13608,7 @@
         <v>88</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="L99" t="s" s="2">
         <v>301</v>
@@ -13690,10 +13676,10 @@
         <v>87</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>199</v>
+        <v>77</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>456</v>
+        <v>99</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>305</v>
@@ -13710,13 +13696,13 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="B100" t="s" s="2">
         <v>223</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="D100" t="s" s="2">
         <v>77</v>
@@ -13826,7 +13812,7 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="B101" t="s" s="2">
         <v>240</v>
@@ -13938,7 +13924,7 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="B102" t="s" s="2">
         <v>242</v>
@@ -14032,7 +14018,7 @@
         <v>79</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>199</v>
+        <v>77</v>
       </c>
       <c r="AJ102" t="s" s="2">
         <v>116</v>
@@ -14041,7 +14027,7 @@
         <v>77</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>190</v>
+        <v>105</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>77</v>
@@ -14052,7 +14038,7 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="B103" t="s" s="2">
         <v>244</v>
@@ -14148,7 +14134,7 @@
         <v>87</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>199</v>
+        <v>77</v>
       </c>
       <c r="AJ103" t="s" s="2">
         <v>99</v>
@@ -14168,7 +14154,7 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="B104" t="s" s="2">
         <v>256</v>
@@ -14216,7 +14202,7 @@
         <v>77</v>
       </c>
       <c r="S104" t="s" s="2">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="T104" t="s" s="2">
         <v>77</v>
@@ -14264,7 +14250,7 @@
         <v>87</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>199</v>
+        <v>77</v>
       </c>
       <c r="AJ104" t="s" s="2">
         <v>99</v>
@@ -14284,7 +14270,7 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="B105" t="s" s="2">
         <v>268</v>
@@ -14380,7 +14366,7 @@
         <v>87</v>
       </c>
       <c r="AI105" t="s" s="2">
-        <v>199</v>
+        <v>77</v>
       </c>
       <c r="AJ105" t="s" s="2">
         <v>99</v>
@@ -14400,7 +14386,7 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="B106" t="s" s="2">
         <v>280</v>
@@ -14494,7 +14480,7 @@
         <v>87</v>
       </c>
       <c r="AI106" t="s" s="2">
-        <v>199</v>
+        <v>77</v>
       </c>
       <c r="AJ106" t="s" s="2">
         <v>99</v>
@@ -14514,7 +14500,7 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="B107" t="s" s="2">
         <v>290</v>
@@ -14548,9 +14534,7 @@
       <c r="M107" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="N107" t="s" s="2">
-        <v>452</v>
-      </c>
+      <c r="N107" s="2"/>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
         <v>77</v>
@@ -14608,10 +14592,10 @@
         <v>87</v>
       </c>
       <c r="AI107" t="s" s="2">
-        <v>199</v>
+        <v>77</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>453</v>
+        <v>99</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>295</v>
@@ -14628,7 +14612,7 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="B108" t="s" s="2">
         <v>299</v>
@@ -14654,7 +14638,7 @@
         <v>88</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="L108" t="s" s="2">
         <v>301</v>
@@ -14722,10 +14706,10 @@
         <v>87</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>199</v>
+        <v>77</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>456</v>
+        <v>99</v>
       </c>
       <c r="AK108" t="s" s="2">
         <v>305</v>
@@ -14742,10 +14726,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14771,23 +14755,23 @@
         <v>394</v>
       </c>
       <c r="L109" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="M109" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="N109" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="O109" t="s" s="2">
         <v>469</v>
       </c>
-      <c r="M109" t="s" s="2">
+      <c r="P109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q109" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="N109" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="O109" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="P109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q109" t="s" s="2">
-        <v>473</v>
-      </c>
       <c r="R109" t="s" s="2">
         <v>77</v>
       </c>
@@ -14831,7 +14815,7 @@
         <v>77</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>78</v>
@@ -14846,24 +14830,24 @@
         <v>99</v>
       </c>
       <c r="AK109" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="AL109" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="AM109" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="AN109" t="s" s="2">
         <v>474</v>
-      </c>
-      <c r="AL109" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="AM109" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="AN109" t="s" s="2">
-        <v>477</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14889,16 +14873,16 @@
         <v>257</v>
       </c>
       <c r="L110" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="M110" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="N110" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="O110" t="s" s="2">
         <v>479</v>
-      </c>
-      <c r="M110" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="N110" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="O110" t="s" s="2">
-        <v>482</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>77</v>
@@ -14926,16 +14910,16 @@
         <v>157</v>
       </c>
       <c r="Y110" t="s" s="2">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="Z110" t="s" s="2">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB110" t="s" s="2">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AC110" s="2"/>
       <c r="AD110" t="s" s="2">
@@ -14945,7 +14929,7 @@
         <v>114</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>78</v>
@@ -14960,27 +14944,27 @@
         <v>99</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>488</v>
+        <v>485</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="D111" t="s" s="2">
         <v>77</v>
@@ -15005,16 +14989,16 @@
         <v>257</v>
       </c>
       <c r="L111" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="M111" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="N111" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="O111" t="s" s="2">
         <v>479</v>
-      </c>
-      <c r="M111" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="N111" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="O111" t="s" s="2">
-        <v>482</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>77</v>
@@ -15043,7 +15027,7 @@
       </c>
       <c r="Y111" s="2"/>
       <c r="Z111" t="s" s="2">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>77</v>
@@ -15061,7 +15045,7 @@
         <v>77</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>78</v>
@@ -15076,24 +15060,24 @@
         <v>99</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>488</v>
+        <v>485</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15202,10 +15186,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15316,10 +15300,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15432,10 +15416,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15544,10 +15528,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15658,10 +15642,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15774,10 +15758,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -15888,10 +15872,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -15917,7 +15901,7 @@
         <v>167</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="M119" t="s" s="2">
         <v>379</v>
@@ -16002,10 +15986,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16116,10 +16100,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16232,10 +16216,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16348,13 +16332,13 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="D123" t="s" s="2">
         <v>77</v>
@@ -16379,16 +16363,16 @@
         <v>257</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="O123" t="s" s="2">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>77</v>
@@ -16417,7 +16401,7 @@
       </c>
       <c r="Y123" s="2"/>
       <c r="Z123" t="s" s="2">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="AA123" t="s" s="2">
         <v>77</v>
@@ -16435,7 +16419,7 @@
         <v>77</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>78</v>
@@ -16450,24 +16434,24 @@
         <v>99</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="AM123" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>488</v>
+        <v>485</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16576,10 +16560,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -16690,10 +16674,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16806,10 +16790,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -16918,10 +16902,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17032,10 +17016,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17148,10 +17132,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17262,10 +17246,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17291,7 +17275,7 @@
         <v>167</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="M131" t="s" s="2">
         <v>379</v>
@@ -17376,10 +17360,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17490,10 +17474,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -17606,10 +17590,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -17722,13 +17706,13 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="C135" t="s" s="2">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="D135" t="s" s="2">
         <v>77</v>
@@ -17753,16 +17737,16 @@
         <v>257</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="O135" t="s" s="2">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>77</v>
@@ -17791,7 +17775,7 @@
       </c>
       <c r="Y135" s="2"/>
       <c r="Z135" t="s" s="2">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="AA135" t="s" s="2">
         <v>77</v>
@@ -17809,7 +17793,7 @@
         <v>77</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>78</v>
@@ -17824,24 +17808,24 @@
         <v>99</v>
       </c>
       <c r="AK135" t="s" s="2">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="AL135" t="s" s="2">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="AM135" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AN135" t="s" s="2">
-        <v>488</v>
+        <v>485</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -17950,10 +17934,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18064,10 +18048,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18180,10 +18164,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18292,10 +18276,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -18406,10 +18390,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -18522,10 +18506,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -18636,10 +18620,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -18665,7 +18649,7 @@
         <v>167</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="M143" t="s" s="2">
         <v>379</v>
@@ -18750,10 +18734,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -18864,10 +18848,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -18980,10 +18964,10 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -19096,10 +19080,10 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -19125,16 +19109,16 @@
         <v>101</v>
       </c>
       <c r="L147" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="M147" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="N147" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="O147" t="s" s="2">
         <v>546</v>
-      </c>
-      <c r="M147" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="N147" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="O147" t="s" s="2">
-        <v>549</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>77</v>
@@ -19183,7 +19167,7 @@
         <v>77</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>78</v>
@@ -19198,13 +19182,13 @@
         <v>99</v>
       </c>
       <c r="AK147" t="s" s="2">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="AL147" t="s" s="2">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="AM147" t="s" s="2">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="AN147" t="s" s="2">
         <v>77</v>
@@ -19212,10 +19196,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -19241,16 +19225,16 @@
         <v>101</v>
       </c>
       <c r="L148" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="M148" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="N148" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="O148" t="s" s="2">
         <v>554</v>
-      </c>
-      <c r="M148" t="s" s="2">
-        <v>555</v>
-      </c>
-      <c r="N148" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="O148" t="s" s="2">
-        <v>557</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>77</v>
@@ -19299,7 +19283,7 @@
         <v>77</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>78</v>
@@ -19317,7 +19301,7 @@
         <v>77</v>
       </c>
       <c r="AL148" t="s" s="2">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="AM148" t="s" s="2">
         <v>77</v>
@@ -19328,10 +19312,10 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -19354,19 +19338,19 @@
         <v>77</v>
       </c>
       <c r="K149" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="L149" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="M149" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="N149" t="s" s="2">
         <v>559</v>
       </c>
-      <c r="L149" t="s" s="2">
+      <c r="O149" t="s" s="2">
         <v>560</v>
-      </c>
-      <c r="M149" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="N149" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="O149" t="s" s="2">
-        <v>563</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>77</v>
@@ -19415,7 +19399,7 @@
         <v>77</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>78</v>
@@ -19427,16 +19411,16 @@
         <v>199</v>
       </c>
       <c r="AJ149" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="AK149" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="AL149" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="AM149" t="s" s="2">
         <v>564</v>
-      </c>
-      <c r="AK149" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="AL149" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="AM149" t="s" s="2">
-        <v>567</v>
       </c>
       <c r="AN149" t="s" s="2">
         <v>77</v>
@@ -19444,10 +19428,10 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -19470,19 +19454,19 @@
         <v>77</v>
       </c>
       <c r="K150" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="L150" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="M150" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="N150" t="s" s="2">
         <v>569</v>
       </c>
-      <c r="L150" t="s" s="2">
+      <c r="O150" t="s" s="2">
         <v>570</v>
-      </c>
-      <c r="M150" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="N150" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="O150" t="s" s="2">
-        <v>573</v>
       </c>
       <c r="P150" t="s" s="2">
         <v>77</v>
@@ -19531,7 +19515,7 @@
         <v>77</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>78</v>
@@ -19543,16 +19527,16 @@
         <v>199</v>
       </c>
       <c r="AJ150" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="AK150" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="AL150" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="AM150" t="s" s="2">
         <v>574</v>
-      </c>
-      <c r="AK150" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="AL150" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="AM150" t="s" s="2">
-        <v>577</v>
       </c>
       <c r="AN150" t="s" s="2">
         <v>77</v>
@@ -19560,10 +19544,10 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -19586,17 +19570,17 @@
         <v>88</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="N151" s="2"/>
       <c r="O151" t="s" s="2">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="P151" t="s" s="2">
         <v>77</v>
@@ -19645,7 +19629,7 @@
         <v>77</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>78</v>
@@ -19660,10 +19644,10 @@
         <v>99</v>
       </c>
       <c r="AK151" t="s" s="2">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="AL151" t="s" s="2">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="AM151" t="s" s="2">
         <v>105</v>
@@ -19674,10 +19658,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -19786,10 +19770,10 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -19900,10 +19884,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -19929,13 +19913,13 @@
         <v>101</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="O154" s="2"/>
       <c r="P154" t="s" s="2">
@@ -19985,7 +19969,7 @@
         <v>77</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>78</v>
@@ -19994,7 +19978,7 @@
         <v>87</v>
       </c>
       <c r="AI154" t="s" s="2">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="AJ154" t="s" s="2">
         <v>99</v>
@@ -20014,10 +19998,10 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -20043,13 +20027,13 @@
         <v>129</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="O155" s="2"/>
       <c r="P155" t="s" s="2">
@@ -20079,7 +20063,7 @@
       </c>
       <c r="Y155" s="2"/>
       <c r="Z155" t="s" s="2">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="AA155" t="s" s="2">
         <v>77</v>
@@ -20097,7 +20081,7 @@
         <v>77</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>78</v>
@@ -20126,10 +20110,10 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -20155,13 +20139,13 @@
         <v>225</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="O156" s="2"/>
       <c r="P156" t="s" s="2">
@@ -20211,7 +20195,7 @@
         <v>77</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>78</v>
@@ -20229,7 +20213,7 @@
         <v>77</v>
       </c>
       <c r="AL156" t="s" s="2">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="AM156" t="s" s="2">
         <v>77</v>
@@ -20240,10 +20224,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -20269,13 +20253,13 @@
         <v>101</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="O157" s="2"/>
       <c r="P157" t="s" s="2">
@@ -20325,7 +20309,7 @@
         <v>77</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>78</v>
@@ -20354,10 +20338,10 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -20380,19 +20364,19 @@
         <v>77</v>
       </c>
       <c r="K158" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="L158" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="M158" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="N158" t="s" s="2">
         <v>609</v>
       </c>
-      <c r="L158" t="s" s="2">
+      <c r="O158" t="s" s="2">
         <v>610</v>
-      </c>
-      <c r="M158" t="s" s="2">
-        <v>611</v>
-      </c>
-      <c r="N158" t="s" s="2">
-        <v>612</v>
-      </c>
-      <c r="O158" t="s" s="2">
-        <v>613</v>
       </c>
       <c r="P158" t="s" s="2">
         <v>77</v>
@@ -20441,7 +20425,7 @@
         <v>77</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>78</v>
@@ -20459,7 +20443,7 @@
         <v>77</v>
       </c>
       <c r="AL158" t="s" s="2">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="AM158" t="s" s="2">
         <v>77</v>
@@ -20470,10 +20454,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -20582,10 +20566,10 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -20696,14 +20680,14 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="E161" s="2"/>
       <c r="F161" t="s" s="2">
@@ -20725,10 +20709,10 @@
         <v>108</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="N161" t="s" s="2">
         <v>111</v>
@@ -20783,7 +20767,7 @@
         <v>77</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>78</v>
@@ -20812,10 +20796,10 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -20841,14 +20825,14 @@
         <v>257</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" t="s" s="2">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="P162" t="s" s="2">
         <v>77</v>
@@ -20876,10 +20860,10 @@
         <v>149</v>
       </c>
       <c r="Y162" t="s" s="2">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="Z162" t="s" s="2">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="AA162" t="s" s="2">
         <v>77</v>
@@ -20897,7 +20881,7 @@
         <v>77</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>78</v>
@@ -20915,7 +20899,7 @@
         <v>77</v>
       </c>
       <c r="AL162" t="s" s="2">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="AM162" t="s" s="2">
         <v>77</v>
@@ -20926,10 +20910,10 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -20952,17 +20936,17 @@
         <v>77</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="N163" s="2"/>
       <c r="O163" t="s" s="2">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>77</v>
@@ -21011,7 +20995,7 @@
         <v>77</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>78</v>
@@ -21026,10 +21010,10 @@
         <v>99</v>
       </c>
       <c r="AK163" t="s" s="2">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AL163" t="s" s="2">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="AM163" t="s" s="2">
         <v>77</v>
@@ -21040,10 +21024,10 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -21066,17 +21050,17 @@
         <v>77</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="N164" s="2"/>
       <c r="O164" t="s" s="2">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="P164" t="s" s="2">
         <v>77</v>
@@ -21125,7 +21109,7 @@
         <v>77</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>78</v>
@@ -21137,16 +21121,16 @@
         <v>199</v>
       </c>
       <c r="AJ164" t="s" s="2">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="AK164" t="s" s="2">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="AL164" t="s" s="2">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="AM164" t="s" s="2">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="AN164" t="s" s="2">
         <v>77</v>
@@ -21154,10 +21138,10 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -21180,19 +21164,19 @@
         <v>77</v>
       </c>
       <c r="K165" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="L165" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="M165" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="N165" t="s" s="2">
         <v>569</v>
       </c>
-      <c r="L165" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="M165" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="N165" t="s" s="2">
-        <v>572</v>
-      </c>
       <c r="O165" t="s" s="2">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="P165" t="s" s="2">
         <v>77</v>
@@ -21241,7 +21225,7 @@
         <v>77</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>78</v>
@@ -21256,13 +21240,13 @@
         <v>99</v>
       </c>
       <c r="AK165" t="s" s="2">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="AL165" t="s" s="2">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="AM165" t="s" s="2">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="AN165" t="s" s="2">
         <v>77</v>
@@ -21270,10 +21254,10 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -21296,17 +21280,17 @@
         <v>77</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" t="s" s="2">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="P166" t="s" s="2">
         <v>77</v>
@@ -21355,7 +21339,7 @@
         <v>77</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>78</v>

--- a/main/ig/StructureDefinition-dmi-organization-ej.xlsx
+++ b/main/ig/StructureDefinition-dmi-organization-ej.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T10:22:34+00:00</t>
+    <t>2026-03-05T10:23:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-dmi-organization-ej.xlsx
+++ b/main/ig/StructureDefinition-dmi-organization-ej.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6047" uniqueCount="643">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6049" uniqueCount="646">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T10:23:55+00:00</t>
+    <t>2026-03-05T10:25:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1431,11 +1431,23 @@
     <t>Organization.identifier:numeroTVAIntracommunautaire.period</t>
   </si>
   <si>
+    <t>A Period specifies a range of time; the context of use will specify whether the entire range applies (e.g. "the patient was an inpatient of the hospital for this time range") or one value from the range applies (e.g. "give to the patient between these two times").
+Period is not used for a duration (a measure of elapsed time). See [Duration](http://hl7.org/fhir/R4/datatypes.html#Duration).</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+per-1:If present, start SHALL have a lower value than end {start.hasValue().not() or end.hasValue().not() or (start &lt;= end)}</t>
+  </si>
+  <si>
     <t>Organization.identifier:numeroTVAIntracommunautaire.assigner</t>
   </si>
   <si>
     <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
   </si>
   <si>
     <t>Organization.identifier:numeroSRN</t>
@@ -12988,7 +13000,7 @@
         <v>79</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="AJ93" t="s" s="2">
         <v>116</v>
@@ -12997,7 +13009,7 @@
         <v>77</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>105</v>
+        <v>190</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>77</v>
@@ -13104,7 +13116,7 @@
         <v>87</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="AJ94" t="s" s="2">
         <v>99</v>
@@ -13220,7 +13232,7 @@
         <v>87</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="AJ95" t="s" s="2">
         <v>99</v>
@@ -13336,7 +13348,7 @@
         <v>87</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="AJ96" t="s" s="2">
         <v>99</v>
@@ -13450,7 +13462,7 @@
         <v>87</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="AJ97" t="s" s="2">
         <v>99</v>
@@ -13504,7 +13516,9 @@
       <c r="M98" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="N98" s="2"/>
+      <c r="N98" t="s" s="2">
+        <v>452</v>
+      </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>77</v>
@@ -13562,10 +13576,10 @@
         <v>87</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>99</v>
+        <v>453</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>295</v>
@@ -13582,7 +13596,7 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B99" t="s" s="2">
         <v>299</v>
@@ -13608,7 +13622,7 @@
         <v>88</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="L99" t="s" s="2">
         <v>301</v>
@@ -13676,10 +13690,10 @@
         <v>87</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>99</v>
+        <v>456</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>305</v>
@@ -13696,13 +13710,13 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="B100" t="s" s="2">
         <v>223</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D100" t="s" s="2">
         <v>77</v>
@@ -13812,7 +13826,7 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="B101" t="s" s="2">
         <v>240</v>
@@ -13924,7 +13938,7 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="B102" t="s" s="2">
         <v>242</v>
@@ -14018,7 +14032,7 @@
         <v>79</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="AJ102" t="s" s="2">
         <v>116</v>
@@ -14027,7 +14041,7 @@
         <v>77</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>105</v>
+        <v>190</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>77</v>
@@ -14038,7 +14052,7 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="B103" t="s" s="2">
         <v>244</v>
@@ -14134,7 +14148,7 @@
         <v>87</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="AJ103" t="s" s="2">
         <v>99</v>
@@ -14154,7 +14168,7 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="B104" t="s" s="2">
         <v>256</v>
@@ -14202,7 +14216,7 @@
         <v>77</v>
       </c>
       <c r="S104" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="T104" t="s" s="2">
         <v>77</v>
@@ -14250,7 +14264,7 @@
         <v>87</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="AJ104" t="s" s="2">
         <v>99</v>
@@ -14270,7 +14284,7 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="B105" t="s" s="2">
         <v>268</v>
@@ -14366,7 +14380,7 @@
         <v>87</v>
       </c>
       <c r="AI105" t="s" s="2">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="AJ105" t="s" s="2">
         <v>99</v>
@@ -14386,7 +14400,7 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="B106" t="s" s="2">
         <v>280</v>
@@ -14480,7 +14494,7 @@
         <v>87</v>
       </c>
       <c r="AI106" t="s" s="2">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="AJ106" t="s" s="2">
         <v>99</v>
@@ -14500,7 +14514,7 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="B107" t="s" s="2">
         <v>290</v>
@@ -14534,7 +14548,9 @@
       <c r="M107" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="N107" s="2"/>
+      <c r="N107" t="s" s="2">
+        <v>452</v>
+      </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
         <v>77</v>
@@ -14592,10 +14608,10 @@
         <v>87</v>
       </c>
       <c r="AI107" t="s" s="2">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>99</v>
+        <v>453</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>295</v>
@@ -14612,7 +14628,7 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="B108" t="s" s="2">
         <v>299</v>
@@ -14638,7 +14654,7 @@
         <v>88</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="L108" t="s" s="2">
         <v>301</v>
@@ -14706,10 +14722,10 @@
         <v>87</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>99</v>
+        <v>456</v>
       </c>
       <c r="AK108" t="s" s="2">
         <v>305</v>
@@ -14726,10 +14742,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14755,67 +14771,67 @@
         <v>394</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="N109" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="O109" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="P109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q109" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="R109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF109" t="s" s="2">
         <v>468</v>
-      </c>
-      <c r="O109" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="P109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q109" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="R109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF109" t="s" s="2">
-        <v>465</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>78</v>
@@ -14830,24 +14846,24 @@
         <v>99</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14873,16 +14889,16 @@
         <v>257</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>77</v>
@@ -14910,16 +14926,16 @@
         <v>157</v>
       </c>
       <c r="Y110" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="Z110" t="s" s="2">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB110" t="s" s="2">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="AC110" s="2"/>
       <c r="AD110" t="s" s="2">
@@ -14929,7 +14945,7 @@
         <v>114</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>78</v>
@@ -14944,27 +14960,27 @@
         <v>99</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="D111" t="s" s="2">
         <v>77</v>
@@ -14989,16 +15005,16 @@
         <v>257</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>77</v>
@@ -15027,7 +15043,7 @@
       </c>
       <c r="Y111" s="2"/>
       <c r="Z111" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>77</v>
@@ -15045,7 +15061,7 @@
         <v>77</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>78</v>
@@ -15060,24 +15076,24 @@
         <v>99</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15186,10 +15202,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15300,10 +15316,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15416,10 +15432,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15528,10 +15544,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15642,10 +15658,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15758,10 +15774,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -15872,10 +15888,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -15901,7 +15917,7 @@
         <v>167</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="M119" t="s" s="2">
         <v>379</v>
@@ -15986,10 +16002,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16100,10 +16116,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16216,10 +16232,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16332,13 +16348,13 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="D123" t="s" s="2">
         <v>77</v>
@@ -16363,16 +16379,16 @@
         <v>257</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="O123" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>77</v>
@@ -16401,7 +16417,7 @@
       </c>
       <c r="Y123" s="2"/>
       <c r="Z123" t="s" s="2">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="AA123" t="s" s="2">
         <v>77</v>
@@ -16419,7 +16435,7 @@
         <v>77</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>78</v>
@@ -16434,24 +16450,24 @@
         <v>99</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="AM123" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16560,10 +16576,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -16674,10 +16690,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16790,10 +16806,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -16902,10 +16918,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17016,10 +17032,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17132,10 +17148,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17246,10 +17262,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17275,7 +17291,7 @@
         <v>167</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="M131" t="s" s="2">
         <v>379</v>
@@ -17360,10 +17376,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17474,10 +17490,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -17590,10 +17606,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -17706,13 +17722,13 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="C135" t="s" s="2">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="D135" t="s" s="2">
         <v>77</v>
@@ -17737,16 +17753,16 @@
         <v>257</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="O135" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>77</v>
@@ -17775,7 +17791,7 @@
       </c>
       <c r="Y135" s="2"/>
       <c r="Z135" t="s" s="2">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="AA135" t="s" s="2">
         <v>77</v>
@@ -17793,7 +17809,7 @@
         <v>77</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>78</v>
@@ -17808,24 +17824,24 @@
         <v>99</v>
       </c>
       <c r="AK135" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="AL135" t="s" s="2">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="AM135" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AN135" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -17934,10 +17950,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18048,10 +18064,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18164,10 +18180,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18276,10 +18292,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -18390,10 +18406,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -18506,10 +18522,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -18620,10 +18636,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -18649,7 +18665,7 @@
         <v>167</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="M143" t="s" s="2">
         <v>379</v>
@@ -18734,10 +18750,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -18848,10 +18864,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -18964,10 +18980,10 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -19080,10 +19096,10 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -19109,16 +19125,16 @@
         <v>101</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="O147" t="s" s="2">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>77</v>
@@ -19167,7 +19183,7 @@
         <v>77</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>78</v>
@@ -19182,13 +19198,13 @@
         <v>99</v>
       </c>
       <c r="AK147" t="s" s="2">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="AL147" t="s" s="2">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="AM147" t="s" s="2">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="AN147" t="s" s="2">
         <v>77</v>
@@ -19196,10 +19212,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -19225,16 +19241,16 @@
         <v>101</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="O148" t="s" s="2">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>77</v>
@@ -19283,7 +19299,7 @@
         <v>77</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>78</v>
@@ -19301,7 +19317,7 @@
         <v>77</v>
       </c>
       <c r="AL148" t="s" s="2">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="AM148" t="s" s="2">
         <v>77</v>
@@ -19312,10 +19328,10 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -19338,19 +19354,19 @@
         <v>77</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="O149" t="s" s="2">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>77</v>
@@ -19399,7 +19415,7 @@
         <v>77</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>78</v>
@@ -19411,16 +19427,16 @@
         <v>199</v>
       </c>
       <c r="AJ149" t="s" s="2">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="AK149" t="s" s="2">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="AL149" t="s" s="2">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="AM149" t="s" s="2">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="AN149" t="s" s="2">
         <v>77</v>
@@ -19428,10 +19444,10 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -19454,19 +19470,19 @@
         <v>77</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="O150" t="s" s="2">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="P150" t="s" s="2">
         <v>77</v>
@@ -19515,7 +19531,7 @@
         <v>77</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>78</v>
@@ -19527,16 +19543,16 @@
         <v>199</v>
       </c>
       <c r="AJ150" t="s" s="2">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="AK150" t="s" s="2">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="AL150" t="s" s="2">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="AM150" t="s" s="2">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="AN150" t="s" s="2">
         <v>77</v>
@@ -19544,10 +19560,10 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -19570,17 +19586,17 @@
         <v>88</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="N151" s="2"/>
       <c r="O151" t="s" s="2">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="P151" t="s" s="2">
         <v>77</v>
@@ -19629,7 +19645,7 @@
         <v>77</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>78</v>
@@ -19644,10 +19660,10 @@
         <v>99</v>
       </c>
       <c r="AK151" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="AL151" t="s" s="2">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="AM151" t="s" s="2">
         <v>105</v>
@@ -19658,10 +19674,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -19770,10 +19786,10 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -19884,10 +19900,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -19913,13 +19929,13 @@
         <v>101</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="O154" s="2"/>
       <c r="P154" t="s" s="2">
@@ -19969,7 +19985,7 @@
         <v>77</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>78</v>
@@ -19978,7 +19994,7 @@
         <v>87</v>
       </c>
       <c r="AI154" t="s" s="2">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="AJ154" t="s" s="2">
         <v>99</v>
@@ -19998,10 +20014,10 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -20027,13 +20043,13 @@
         <v>129</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="O155" s="2"/>
       <c r="P155" t="s" s="2">
@@ -20063,7 +20079,7 @@
       </c>
       <c r="Y155" s="2"/>
       <c r="Z155" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="AA155" t="s" s="2">
         <v>77</v>
@@ -20081,7 +20097,7 @@
         <v>77</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>78</v>
@@ -20110,10 +20126,10 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -20139,13 +20155,13 @@
         <v>225</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="O156" s="2"/>
       <c r="P156" t="s" s="2">
@@ -20195,7 +20211,7 @@
         <v>77</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>78</v>
@@ -20213,7 +20229,7 @@
         <v>77</v>
       </c>
       <c r="AL156" t="s" s="2">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="AM156" t="s" s="2">
         <v>77</v>
@@ -20224,10 +20240,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -20253,13 +20269,13 @@
         <v>101</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="O157" s="2"/>
       <c r="P157" t="s" s="2">
@@ -20309,7 +20325,7 @@
         <v>77</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>78</v>
@@ -20338,10 +20354,10 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -20364,19 +20380,19 @@
         <v>77</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="O158" t="s" s="2">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="P158" t="s" s="2">
         <v>77</v>
@@ -20425,7 +20441,7 @@
         <v>77</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>78</v>
@@ -20443,7 +20459,7 @@
         <v>77</v>
       </c>
       <c r="AL158" t="s" s="2">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="AM158" t="s" s="2">
         <v>77</v>
@@ -20454,10 +20470,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -20566,10 +20582,10 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -20680,14 +20696,14 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="E161" s="2"/>
       <c r="F161" t="s" s="2">
@@ -20709,10 +20725,10 @@
         <v>108</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="N161" t="s" s="2">
         <v>111</v>
@@ -20767,7 +20783,7 @@
         <v>77</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>78</v>
@@ -20796,10 +20812,10 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -20825,14 +20841,14 @@
         <v>257</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" t="s" s="2">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="P162" t="s" s="2">
         <v>77</v>
@@ -20860,10 +20876,10 @@
         <v>149</v>
       </c>
       <c r="Y162" t="s" s="2">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="Z162" t="s" s="2">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="AA162" t="s" s="2">
         <v>77</v>
@@ -20881,7 +20897,7 @@
         <v>77</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>78</v>
@@ -20899,7 +20915,7 @@
         <v>77</v>
       </c>
       <c r="AL162" t="s" s="2">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="AM162" t="s" s="2">
         <v>77</v>
@@ -20910,10 +20926,10 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -20936,17 +20952,17 @@
         <v>77</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="N163" s="2"/>
       <c r="O163" t="s" s="2">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>77</v>
@@ -20995,7 +21011,7 @@
         <v>77</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>78</v>
@@ -21010,10 +21026,10 @@
         <v>99</v>
       </c>
       <c r="AK163" t="s" s="2">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="AL163" t="s" s="2">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="AM163" t="s" s="2">
         <v>77</v>
@@ -21024,10 +21040,10 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -21050,17 +21066,17 @@
         <v>77</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="N164" s="2"/>
       <c r="O164" t="s" s="2">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="P164" t="s" s="2">
         <v>77</v>
@@ -21109,7 +21125,7 @@
         <v>77</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>78</v>
@@ -21121,16 +21137,16 @@
         <v>199</v>
       </c>
       <c r="AJ164" t="s" s="2">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="AK164" t="s" s="2">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="AL164" t="s" s="2">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="AM164" t="s" s="2">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="AN164" t="s" s="2">
         <v>77</v>
@@ -21138,10 +21154,10 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -21164,19 +21180,19 @@
         <v>77</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="O165" t="s" s="2">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="P165" t="s" s="2">
         <v>77</v>
@@ -21225,7 +21241,7 @@
         <v>77</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>78</v>
@@ -21240,13 +21256,13 @@
         <v>99</v>
       </c>
       <c r="AK165" t="s" s="2">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="AL165" t="s" s="2">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="AM165" t="s" s="2">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="AN165" t="s" s="2">
         <v>77</v>
@@ -21254,10 +21270,10 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -21280,17 +21296,17 @@
         <v>77</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" t="s" s="2">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="P166" t="s" s="2">
         <v>77</v>
@@ -21339,7 +21355,7 @@
         <v>77</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>78</v>
